--- a/final_data_pipeline/output/311422_elec_options.xlsx
+++ b/final_data_pipeline/output/311422_elec_options.xlsx
@@ -1418,7 +1418,7 @@
         <v>56</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1513,7 +1513,7 @@
         <v>56</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1608,7 +1608,7 @@
         <v>56</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1703,7 +1703,7 @@
         <v>56</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1798,7 +1798,7 @@
         <v>56</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1893,7 +1893,7 @@
         <v>56</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -1988,7 +1988,7 @@
         <v>56</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2083,7 +2083,7 @@
         <v>56</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2178,7 +2178,7 @@
         <v>56</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2273,7 +2273,7 @@
         <v>56</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2368,7 +2368,7 @@
         <v>56</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2463,7 +2463,7 @@
         <v>56</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2558,7 +2558,7 @@
         <v>56</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2653,7 +2653,7 @@
         <v>56</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2748,7 +2748,7 @@
         <v>56</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2843,7 +2843,7 @@
         <v>56</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -2938,7 +2938,7 @@
         <v>56</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3033,7 +3033,7 @@
         <v>56</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -3128,7 +3128,7 @@
         <v>56</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE27">
         <v>8000</v>
@@ -3223,7 +3223,7 @@
         <v>56</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE28">
         <v>8000</v>
@@ -3318,7 +3318,7 @@
         <v>56</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE29">
         <v>8000</v>
@@ -3413,7 +3413,7 @@
         <v>56</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3508,7 +3508,7 @@
         <v>56</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3603,7 +3603,7 @@
         <v>56</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3698,7 +3698,7 @@
         <v>56</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -3793,7 +3793,7 @@
         <v>56</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -3888,7 +3888,7 @@
         <v>56</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -3983,7 +3983,7 @@
         <v>56</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE36">
         <v>8000</v>
